--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N11" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>CD Universidad Católica</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>LDU Quito</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>SD Aucas</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Aucas</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU11"/>
+  <dimension ref="A1:AU5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46217.79166666666</v>
+        <v>46217.77083333334</v>
       </c>
     </row>
     <row r="3">
@@ -837,12 +837,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46217.875</v>
+        <v>46217.79166666666</v>
       </c>
     </row>
     <row r="4">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CD Universidad Católica</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>LDU Quito</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1305,960 +1305,6 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46217.875</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Orense SC</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CS Emelec</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="3" t="n">
-        <v>46217.875</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Leones del Norte</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Deportivo Cuenca</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" s="3" t="n">
-        <v>46217.875</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SD Aucas</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CSD Independiente del Valle</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" s="3" t="n">
-        <v>46217.875</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Manta FC</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Delfin SC</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" s="3" t="n">
-        <v>46217.875</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Guayaquil City FC</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" s="3" t="n">
-        <v>46217.875</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Blooming</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Gualberto Villarroel SJ</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P11" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" s="3" t="n">
         <v>46217.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -1247,10 +1247,10 @@
         <v>2.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AE5" t="n">
         <v>1.3</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.06</v>
+        <v>1.44</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>4.86</v>
       </c>
       <c r="P2" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46217.77083333334</v>
+        <v>46217.35763888889</v>
       </c>
     </row>
     <row r="3">
@@ -837,12 +837,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46217.79166666666</v>
+        <v>46217.77083333334</v>
       </c>
     </row>
     <row r="4">
@@ -996,12 +996,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46217.875</v>
+        <v>46217.79166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1155,156 +1155,315 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="3" t="n">
+        <v>46217.875</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Blooming</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr">
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="N6" t="n">
         <v>1.4</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O6" t="n">
         <v>4.5</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P6" t="n">
         <v>5.75</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q6" t="n">
         <v>1.83</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R6" t="n">
         <v>2.63</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>1.22</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>3.5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>2.08</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V6" t="n">
         <v>1.66</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W6" t="n">
         <v>1.15</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X6" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y6" t="n">
         <v>1.09</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z6" t="n">
         <v>5.3</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA6" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB6" t="n">
         <v>2.7</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC6" t="n">
         <v>2.1</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD6" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF6" t="n">
         <v>1.56</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG6" t="n">
         <v>2.25</v>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AJ6" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK6" t="n">
         <v>2.57</v>
       </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" s="3" t="n">
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="3" t="n">
         <v>46217.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -734,22 +734,22 @@
         <v>5.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
         <v>2.6</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T2" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="U2" t="n">
         <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W2" t="n">
         <v>1.19</v>
@@ -761,19 +761,19 @@
         <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.22</v>
+        <v>6.28</v>
       </c>
       <c r="AA2" t="n">
         <v>1.43</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE2" t="n">
         <v>1.25</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK2" t="n">
         <v>2.48</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -758,19 +758,19 @@
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.28</v>
+        <v>5.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AB2" t="n">
         <v>2.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AD2" t="n">
         <v>1.71</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -920,13 +920,13 @@
         <v>1.37</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="AA3" t="n">
         <v>2.13</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC3" t="n">
         <v>4.54</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -893,22 +893,22 @@
         <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
         <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
@@ -917,31 +917,31 @@
         <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB3" t="n">
         <v>1.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.54</v>
+        <v>3.79</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="O2" t="n">
-        <v>4.86</v>
+        <v>4.76</v>
       </c>
       <c r="P2" t="n">
         <v>5.5</v>
@@ -743,7 +743,7 @@
         <v>1.21</v>
       </c>
       <c r="T2" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="U2" t="n">
         <v>1.95</v>
@@ -758,10 +758,10 @@
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
         <v>1.44</v>
@@ -770,7 +770,7 @@
         <v>2.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="AD2" t="n">
         <v>1.71</v>
@@ -896,7 +896,7 @@
         <v>2.68</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="S3" t="n">
         <v>1.42</v>
@@ -905,10 +905,10 @@
         <v>2.75</v>
       </c>
       <c r="U3" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
         <v>1.04</v>
@@ -917,22 +917,22 @@
         <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.25</v>
+        <v>3.06</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
         <v>1.66</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.79</v>
+        <v>4.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
         <v>1.07</v>
@@ -941,7 +941,7 @@
         <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="O5" t="n">
         <v>2.9</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="O2" t="n">
-        <v>4.76</v>
+        <v>4.96</v>
       </c>
       <c r="P2" t="n">
         <v>5.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
         <v>2.6</v>
@@ -761,7 +761,7 @@
         <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1.44</v>
@@ -770,7 +770,7 @@
         <v>2.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD2" t="n">
         <v>1.71</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK2" t="n">
         <v>2.48</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -728,13 +728,13 @@
         <v>1.44</v>
       </c>
       <c r="O2" t="n">
-        <v>4.96</v>
+        <v>4.75</v>
       </c>
       <c r="P2" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
         <v>2.6</v>
@@ -749,7 +749,7 @@
         <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="W2" t="n">
         <v>1.19</v>
@@ -761,7 +761,7 @@
         <v>1.13</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA2" t="n">
         <v>1.44</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -884,25 +884,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="R3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
         <v>2.96</v>
@@ -923,19 +923,19 @@
         <v>3.06</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.36</v>
+        <v>3.65</v>
       </c>
       <c r="AD3" t="n">
         <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF3" t="n">
         <v>1.84</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="O5" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -893,7 +893,7 @@
         <v>3.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="R3" t="n">
         <v>2.1</v>
@@ -905,13 +905,13 @@
         <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1.03</v>
@@ -932,7 +932,7 @@
         <v>3.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE3" t="n">
         <v>1.04</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,10 +1202,10 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="P5" t="n">
         <v>3.1</v>
@@ -1217,13 +1217,13 @@
         <v>1.77</v>
       </c>
       <c r="S5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="U5" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="V5" t="n">
         <v>1.18</v>
@@ -1232,13 +1232,13 @@
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AA5" t="n">
         <v>2.7</v>
@@ -1247,10 +1247,10 @@
         <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.26</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
         <v>1.01</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -728,22 +728,22 @@
         <v>1.44</v>
       </c>
       <c r="O2" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P2" t="n">
-        <v>5.25</v>
+        <v>5.64</v>
       </c>
       <c r="Q2" t="n">
         <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="S2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
         <v>1.95</v>
@@ -758,25 +758,25 @@
         <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="Z2" t="n">
         <v>9.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AB2" t="n">
         <v>2.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AD2" t="n">
         <v>1.71</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF2" t="n">
         <v>1.55</v>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AK2" t="n">
         <v>2.48</v>
@@ -884,31 +884,31 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="O3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P3" t="n">
         <v>3.3</v>
       </c>
-      <c r="P3" t="n">
-        <v>3.42</v>
-      </c>
       <c r="Q3" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
         <v>1.06</v>
@@ -917,31 +917,31 @@
         <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AD3" t="n">
         <v>1.24</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,58 +1202,58 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="O5" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="S5" t="n">
         <v>1.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.5</v>
+        <v>5.71</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
         <v>2.21</v>
@@ -1275,7 +1275,7 @@
         <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -893,7 +893,7 @@
         <v>3.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="R3" t="n">
         <v>2.01</v>
@@ -905,13 +905,13 @@
         <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
         <v>1.03</v>
@@ -920,22 +920,22 @@
         <v>1.35</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AA3" t="n">
         <v>2.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
         <v>3.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF3" t="n">
         <v>1.83</v>
@@ -957,7 +957,7 @@
         <v>1.26</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1205,16 +1205,16 @@
         <v>2.16</v>
       </c>
       <c r="O5" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R5" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="S5" t="n">
         <v>1.62</v>
@@ -1226,7 +1226,7 @@
         <v>3.82</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>
@@ -1235,22 +1235,22 @@
         <v>1.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="Z5" t="n">
         <v>2.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.71</v>
+        <v>4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AE5" t="n">
         <v>1.03</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="O2" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P2" t="n">
-        <v>5.64</v>
+        <v>5.7</v>
       </c>
       <c r="Q2" t="n">
         <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T2" t="n">
         <v>4</v>
@@ -749,40 +749,40 @@
         <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="W2" t="n">
         <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
         <v>2.48</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -896,37 +896,37 @@
         <v>2.63</v>
       </c>
       <c r="R3" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U3" t="n">
         <v>2.9</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W3" t="n">
         <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z3" t="n">
         <v>2.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC3" t="n">
         <v>3.5</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1202,34 +1202,34 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.13</v>
+        <v>3.53</v>
       </c>
       <c r="R5" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="S5" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="V5" t="n">
         <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.1</v>
@@ -1247,10 +1247,10 @@
         <v>1.44</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AE5" t="n">
         <v>1.03</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -728,16 +728,16 @@
         <v>1.4</v>
       </c>
       <c r="O2" t="n">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="P2" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Q2" t="n">
         <v>1.85</v>
       </c>
       <c r="R2" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="S2" t="n">
         <v>1.18</v>
@@ -758,7 +758,7 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z2" t="n">
         <v>6</v>
@@ -776,7 +776,7 @@
         <v>1.75</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF2" t="n">
         <v>1.5</v>
@@ -923,10 +923,10 @@
         <v>2.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
         <v>3.5</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,34 +1202,34 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.53</v>
+        <v>3.79</v>
       </c>
       <c r="R5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
         <v>1.1</v>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O6" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="P6" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R6" t="n">
         <v>2.63</v>
@@ -1382,10 +1382,10 @@
         <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W6" t="n">
         <v>1.15</v>
@@ -1394,10 +1394,10 @@
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AA6" t="n">
         <v>1.44</v>
@@ -1406,19 +1406,19 @@
         <v>2.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -1211,7 +1211,7 @@
         <v>2.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.79</v>
+        <v>3.82</v>
       </c>
       <c r="R5" t="n">
         <v>1.72</v>
@@ -1226,7 +1226,7 @@
         <v>3.92</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
         <v>1.03</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -725,31 +725,31 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="O2" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="P2" t="n">
-        <v>5.9</v>
+        <v>5.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="S2" t="n">
         <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V2" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="W2" t="n">
         <v>1.19</v>
@@ -758,25 +758,25 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1.36</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF2" t="n">
         <v>1.5</v>
@@ -837,27 +837,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P3" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T3" t="n">
         <v>3.3</v>
       </c>
-      <c r="Q3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.59</v>
-      </c>
       <c r="U3" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.95</v>
+        <v>4.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>1.56</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.5</v>
+        <v>2.39</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.69</v>
+        <v>2.28</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -987,7 +987,7 @@
         <v>0</v>
       </c>
       <c r="AU3" s="3" t="n">
-        <v>46217.77083333334</v>
+        <v>46217.5</v>
       </c>
     </row>
     <row r="4">
@@ -996,27 +996,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Inter Club d'Escaldes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>1.75</v>
       </c>
       <c r="O4" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.08</v>
+        <v>2.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.7</v>
+        <v>5.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.19</v>
+        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>46217.79166666666</v>
+        <v>46217.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1155,27 +1155,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>3.78</v>
       </c>
       <c r="P5" t="n">
-        <v>2.7</v>
+        <v>4.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.82</v>
+        <v>1.99</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>2.07</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>3.92</v>
+        <v>2.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.03</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="Z5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.4</v>
       </c>
-      <c r="AA5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC5" t="n">
-        <v>4.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.44</v>
+        <v>2.39</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46217.875</v>
+        <v>46217.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1314,156 +1314,1746 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Riga</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FC Avan Academy</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="3" t="n">
+        <v>46217.58333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Győri ETO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Víkingur Reykjavík</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" s="3" t="n">
+        <v>46217.58333333334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Levski Sofia</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Borac Banja Luka</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="3" t="n">
+        <v>46217.60416666666</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>The New Saints</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sabah</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="3" t="n">
+        <v>46217.60416666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Drita</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kauno Žalgiris</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3" t="n">
+        <v>46217.625</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Shamrock Rovers</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Floriana</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3" t="n">
+        <v>46217.66666666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Europe UEFA Champions League</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tre Fiori</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="3" t="n">
+        <v>46217.66666666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mushuc Runa SC</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>46217.77083333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Real Oruro</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Club Always Ready</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="3" t="n">
+        <v>46217.79166666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="3" t="n">
+        <v>46217.875</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Bolivia LFPB</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Blooming</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Gualberto Villarroel SJ</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="inlineStr">
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="N16" t="n">
         <v>1.44</v>
       </c>
-      <c r="O6" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="O16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1.85</v>
       </c>
-      <c r="R6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="R16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S16" t="n">
         <v>1.22</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T16" t="n">
         <v>3.5</v>
       </c>
-      <c r="U6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="U16" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.15</v>
       </c>
-      <c r="X6" t="n">
+      <c r="X16" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AA6" t="n">
+      <c r="Y16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AA16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AB16" t="n">
         <v>2.7</v>
       </c>
-      <c r="AC6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="AC16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.25</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AF16" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AG16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AI16" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" s="3" t="n">
+      <c r="AJ16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="3" t="n">
         <v>46217.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -702,39 +702,39 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="P2" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
         <v>2.75</v>
@@ -743,7 +743,7 @@
         <v>1.18</v>
       </c>
       <c r="T2" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
         <v>1.91</v>
@@ -761,37 +761,37 @@
         <v>1.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '50', '90+6']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58', '71']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
@@ -804,28 +804,28 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46217.35763888889</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="O3" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="P3" t="n">
-        <v>5.02</v>
+        <v>6.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="V3" t="n">
         <v>1.62</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
         <v>1.14</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.28</v>
+        <v>2.53</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inter Club d'Escaldes</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,31 +1043,31 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="O4" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="P4" t="n">
-        <v>3.9</v>
+        <v>4.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
         <v>1.17</v>
@@ -1076,31 +1076,31 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.85</v>
+        <v>5.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.68</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.99</v>
+        <v>2.13</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Inter Club d'Escaldes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="O5" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="P5" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.99</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.75</v>
+        <v>5.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.4</v>
+        <v>2.71</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.14</v>
+        <v>2.55</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="R6" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
         <v>1.4</v>
@@ -1391,7 +1391,7 @@
         <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
         <v>1.29</v>
@@ -1400,25 +1400,25 @@
         <v>3.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="AD6" t="n">
         <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,34 +1520,34 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
       <c r="S7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
@@ -1559,25 +1559,25 @@
         <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
         <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK7" t="n">
         <v>2.05</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.33</v>
+        <v>5.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.85</v>
+        <v>5.38</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="T8" t="n">
-        <v>2.59</v>
+        <v>3.15</v>
       </c>
       <c r="U8" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.42</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.01</v>
+        <v>1.56</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.62</v>
+        <v>2.38</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.5</v>
+        <v>2.16</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.25</v>
+        <v>1.13</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4.75</v>
+        <v>1.35</v>
       </c>
       <c r="O9" t="n">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>1.77</v>
       </c>
       <c r="R9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF9" t="n">
         <v>2.5</v>
       </c>
-      <c r="S9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="AG9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.11</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.09</v>
+        <v>2.88</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AB10" t="n">
         <v>1.72</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Tre Fiori</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="O11" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="S11" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="T11" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>2.41</v>
+        <v>2.15</v>
       </c>
       <c r="V11" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.5</v>
+        <v>6.05</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tre Fiori</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.13</v>
-      </c>
-      <c r="O12" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.15</v>
       </c>
       <c r="Z12" t="n">
         <v>4.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK12" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="S13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
         <v>2.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
         <v>1.07</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.67</v>
+        <v>3.79</v>
       </c>
       <c r="O14" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.75</v>
+        <v>4.03</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="S14" t="n">
         <v>1.2</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="W14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,28 +2792,28 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.84</v>
+        <v>3.96</v>
       </c>
       <c r="R15" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="S15" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="T15" t="n">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="U15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="V15" t="n">
         <v>1.22</v>
@@ -2822,34 +2822,34 @@
         <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AE15" t="n">
         <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2954,61 +2954,61 @@
         <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>1.85</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="S16" t="n">
         <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.07</v>
+        <v>2.21</v>
       </c>
       <c r="V16" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB16" t="n">
         <v>2.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AE16" t="n">
         <v>1.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -873,14 +873,14 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,12 +945,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['100', '105+1']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['102', '59', '90+1']</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46217.5</v>
@@ -1011,19 +1011,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Inter Club d'Escaldes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1032,118 +1032,118 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="O4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P4" t="n">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.1</v>
+        <v>5.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46217.54166666666</v>
@@ -1170,22 +1170,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inter Club d'Escaldes</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1194,115 +1194,115 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="O5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>4.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.85</v>
+        <v>5.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13', '37']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['69', '84']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46217.54166666666</v>
@@ -1338,26 +1338,26 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '23', '90+4']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46', '63']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46217.58333333334</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>5.5</v>
+        <v>1.35</v>
       </c>
       <c r="O8" t="n">
-        <v>4.4</v>
+        <v>5.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.38</v>
+        <v>1.77</v>
       </c>
       <c r="R8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.5</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG8" t="n">
-        <v>2.16</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.13</v>
+        <v>2.88</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.35</v>
+        <v>5.5</v>
       </c>
       <c r="O9" t="n">
-        <v>5.25</v>
+        <v>4.4</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.77</v>
+        <v>5.38</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="T9" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="U9" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.49</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.2</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.88</v>
+        <v>1.13</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -1011,31 +1011,31 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inter Club d'Escaldes</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="O4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P4" t="n">
-        <v>4.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="R4" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="U4" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.85</v>
+        <v>5.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['13', '37']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['69', '84']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO4" t="n">
         <v>11</v>
       </c>
-      <c r="AN4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>22</v>
-      </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.79</v>
+        <v>1.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.74</v>
+        <v>1.41</v>
       </c>
       <c r="AS4" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="AT4" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46217.54166666666</v>
@@ -1170,31 +1170,31 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Inter Club d'Escaldes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="O5" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P5" t="n">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T5" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V5" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="W5" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.1</v>
+        <v>5.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['13', '37']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>['69', '84']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AN5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP5" t="n">
         <v>6</v>
       </c>
-      <c r="AO5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>1.58</v>
+        <v>2.79</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.41</v>
+        <v>0.74</v>
       </c>
       <c r="AS5" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="AT5" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46217.54166666666</v>
@@ -1329,16 +1329,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -1347,121 +1347,121 @@
         <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.86</v>
+        <v>2.48</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.96</v>
+        <v>2.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>['38', '45+1']</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>['34', '55']</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
         <v>2</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>['14', '23', '90+4']</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>['46', '63']</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>8</v>
-      </c>
       <c r="AN6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO6" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="AS6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT6" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46217.58333333334</v>
@@ -1488,139 +1488,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="O7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R7" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="S7" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="V7" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.48</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.25</v>
+        <v>2.96</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '23', '90+4']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['46', '63']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46217.58333333334</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1668,14 +1668,14 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['48', '59', '65', '85']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46217.60416666666</v>
@@ -1815,26 +1815,26 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28', '43']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
@@ -1917,28 +1917,28 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46217.60416666666</v>
@@ -1974,26 +1974,26 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '53']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['9', '82', '90+4']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
@@ -2076,28 +2076,28 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46217.625</v>
@@ -2124,139 +2124,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tre Fiori</t>
+          <t>Floriana</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="O11" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.15</v>
       </c>
-      <c r="O11" t="n">
-        <v>8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF11" t="n">
-        <v>2.76</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '29', '48', '61', '74']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>6.05</v>
+        <v>3.7</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46217.66666666666</v>
@@ -2283,139 +2283,139 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Floriana</t>
+          <t>Tre Fiori</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="O12" t="n">
-        <v>4.95</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>7.1</v>
+        <v>19</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="S12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T12" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="V12" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.6</v>
+        <v>5.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>2.76</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.8</v>
+        <v>1.39</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '69']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.7</v>
+        <v>6.05</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46217.66666666666</v>

--- a/jogos_2026-07-14.xlsx
+++ b/jogos_2026-07-14.xlsx
@@ -1011,31 +1011,31 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Inter Club d'Escaldes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="O4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="P4" t="n">
-        <v>4.95</v>
+        <v>4.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T4" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="W4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X4" t="n">
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.1</v>
+        <v>5.85</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['13', '37']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>['69', '84']</t>
+          <t>['63']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.56</v>
+        <v>2.1</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AN4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP4" t="n">
         <v>6</v>
       </c>
-      <c r="AO4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>2.79</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.41</v>
+        <v>0.74</v>
       </c>
       <c r="AS4" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="AT4" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46217.54166666666</v>
@@ -1170,31 +1170,31 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inter Club d'Escaldes</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="O5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="P5" t="n">
-        <v>4.33</v>
+        <v>4.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="R5" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T5" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.85</v>
+        <v>5.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['13', '37']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['69', '84']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO5" t="n">
         <v>11</v>
       </c>
-      <c r="AN5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>22</v>
-      </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.79</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.74</v>
+        <v>1.41</v>
       </c>
       <c r="AS5" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="AT5" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46217.54166666666</v>
@@ -1329,16 +1329,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Víkingur Reykjavík</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -1347,13 +1347,13 @@
         <v>2</v>
       </c>
       <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1361,107 +1361,107 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R6" t="n">
-        <v>2.61</v>
+        <v>2.38</v>
       </c>
       <c r="S6" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.64</v>
       </c>
       <c r="V6" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="W6" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.48</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.25</v>
+        <v>2.96</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>['38', '45+1']</t>
+          <t>['14', '23', '90+4']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>['34', '55']</t>
+          <t>['46', '63']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.42</v>
+        <v>2.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="AS6" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AT6" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46217.58333333334</v>
@@ -1488,16 +1488,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>Víkingur Reykjavík</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>2</v>
@@ -1506,121 +1506,121 @@
         <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>2</v>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="O7" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="P7" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.86</v>
+        <v>2.48</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.96</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>['38', '45+1']</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>['34', '55']</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
         <v>2</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>['14', '23', '90+4']</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>['46', '63']</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>8</v>
-      </c>
       <c r="AN7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.6</v>
+        <v>1.42</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="AS7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AT7" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46217.58333333334</v>
@@ -2451,42 +2451,42 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="R13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="S13" t="n">
         <v>1.46</v>
@@ -2495,86 +2495,86 @@
         <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="V13" t="n">
         <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.65</v>
+        <v>4.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '68']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
         <v>1.31</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46217.77083333334</v>
@@ -2613,84 +2613,84 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>3.79</v>
+        <v>3.3</v>
       </c>
       <c r="O14" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.03</v>
+        <v>3.67</v>
       </c>
       <c r="R14" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T14" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="V14" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="W14" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.4</v>
+        <v>7.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.85</v>
+        <v>3.26</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2699,41 +2699,41 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24', '32', '35', '80', '83', '90+2']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46217.79166666666</v>
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.79</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P15" t="n">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.96</v>
+        <v>3.65</v>
       </c>
       <c r="R15" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.3</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2954,61 +2954,61 @@
         <v>1.44</v>
       </c>
       <c r="O16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P16" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="T16" t="n">
         <v>4.2</v>
       </c>
-      <c r="P16" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.6</v>
-      </c>
       <c r="U16" t="n">
-        <v>2.21</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X16" t="n">
         <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z16" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.58</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
